--- a/NOC_MTTR_Report.xlsx
+++ b/NOC_MTTR_Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30611"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adidasgroup.sharepoint.com/sites/connect/Shared Documents/013 Operations/Operational KPI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="13_ncr:1_{B7EE8313-4F3B-4583-ADA7-DDA17030689A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B75AE4FB-856C-4C56-BC12-403AA01BBDEA}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="13_ncr:1_{B7EE8313-4F3B-4583-ADA7-DDA17030689A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4C7E8BA-DB3D-4327-AC18-13513AF5EF72}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F44E7462-D26D-4CE0-8E30-F9E3BFC2560B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{F44E7462-D26D-4CE0-8E30-F9E3BFC2560B}"/>
   </bookViews>
   <sheets>
     <sheet name="NOC_MTTR" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="89">
   <si>
     <t xml:space="preserve">1 - Critical </t>
   </si>
@@ -54,170 +54,263 @@
     <t>5 - Minor</t>
   </si>
   <si>
-    <t>23 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 35 Min</t>
-  </si>
-  <si>
-    <t>3 Hours 18 Min</t>
-  </si>
-  <si>
-    <t>4 Hours 6 Min</t>
-  </si>
-  <si>
-    <t>2 Hours 35 Min</t>
-  </si>
-  <si>
-    <t>38 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 7 Min</t>
-  </si>
-  <si>
-    <t>2 Hours 15 Min</t>
-  </si>
-  <si>
-    <t>2 Hours 31 Min</t>
-  </si>
-  <si>
-    <t>2 Hours 26 Min</t>
+    <t>49 Min</t>
+  </si>
+  <si>
+    <t>55 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 27 Min</t>
+  </si>
+  <si>
+    <t>2 Hours 6 Min</t>
+  </si>
+  <si>
+    <t>2 Hours 56 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 24 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 4 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 36 Min</t>
+  </si>
+  <si>
+    <t>3 Hours 4 Min</t>
+  </si>
+  <si>
+    <t>4 Hours 57 Min</t>
+  </si>
+  <si>
+    <t>2 Hours 25 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 31 Min</t>
+  </si>
+  <si>
+    <t>2 Hours 33 Min</t>
+  </si>
+  <si>
+    <t>10 Hours 47 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 12 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 10 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 41 Min</t>
+  </si>
+  <si>
+    <t>2 Hours 42 Min</t>
+  </si>
+  <si>
+    <t>6 Hours 41 Min</t>
+  </si>
+  <si>
+    <t>57 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 58 Min</t>
+  </si>
+  <si>
+    <t>3 Hours 11 Min</t>
+  </si>
+  <si>
+    <t>5 Hours 26 Min</t>
+  </si>
+  <si>
+    <t>46 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 6 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 37 Min</t>
+  </si>
+  <si>
+    <t>3 Hours 27 Min</t>
+  </si>
+  <si>
+    <t>3 Hours 53 Min</t>
+  </si>
+  <si>
+    <t>21 Min</t>
+  </si>
+  <si>
+    <t>36 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 3 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 43 Min</t>
+  </si>
+  <si>
+    <t>4 Hours 16 Min</t>
+  </si>
+  <si>
+    <t>53 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 13 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 54 Min</t>
+  </si>
+  <si>
+    <t>3 Hours 23 Min</t>
+  </si>
+  <si>
+    <t>48 Min</t>
+  </si>
+  <si>
+    <t>34 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 5 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 46 Min</t>
+  </si>
+  <si>
+    <t>2 Hours 45 Min</t>
+  </si>
+  <si>
+    <t>20 Min</t>
+  </si>
+  <si>
+    <t>28 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 11 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 28 Min</t>
+  </si>
+  <si>
+    <t>27 Min</t>
+  </si>
+  <si>
+    <t>47 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 52 Min</t>
   </si>
   <si>
     <t>32 Min</t>
   </si>
   <si>
-    <t>1 Hour 1 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 22 Min</t>
-  </si>
-  <si>
-    <t>2 Hours 12 Min</t>
-  </si>
-  <si>
-    <t>3 Hours 14 Min</t>
-  </si>
-  <si>
-    <t>49 Min</t>
-  </si>
-  <si>
-    <t>55 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 27 Min</t>
-  </si>
-  <si>
-    <t>2 Hours 6 Min</t>
-  </si>
-  <si>
-    <t>2 Hours 56 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 24 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 4 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 36 Min</t>
-  </si>
-  <si>
-    <t>3 Hours 4 Min</t>
-  </si>
-  <si>
-    <t>4 Hours 57 Min</t>
-  </si>
-  <si>
-    <t>2 Hours 25 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 31 Min</t>
-  </si>
-  <si>
-    <t>2 Hours 33 Min</t>
-  </si>
-  <si>
-    <t>10 Hours 47 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 12 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 10 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 41 Min</t>
-  </si>
-  <si>
-    <t>2 Hours 42 Min</t>
-  </si>
-  <si>
-    <t>6 Hours 41 Min</t>
-  </si>
-  <si>
-    <t>57 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 58 Min</t>
-  </si>
-  <si>
-    <t>3 Hours 11 Min</t>
-  </si>
-  <si>
-    <t>5 Hours 26 Min</t>
-  </si>
-  <si>
-    <t>46 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 6 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 37 Min</t>
-  </si>
-  <si>
-    <t>3 Hours 27 Min</t>
-  </si>
-  <si>
-    <t>3 Hours 53 Min</t>
-  </si>
-  <si>
-    <t>1 Hour 5 Minutes</t>
-  </si>
-  <si>
-    <t>14 Hours 38 Minutes</t>
-  </si>
-  <si>
-    <t>1 Day 16 Hours 12 Minutes</t>
-  </si>
-  <si>
-    <t>15 Hours 15 Minutes</t>
-  </si>
-  <si>
-    <t>17 Hours</t>
-  </si>
-  <si>
-    <t>7 Hours 6 Minutes</t>
-  </si>
-  <si>
-    <t>1 Day 56 Minutes</t>
-  </si>
-  <si>
-    <t>3 Days 16 Hours 29 Minutes</t>
-  </si>
-  <si>
-    <t>22 Hours 18 Minutes</t>
-  </si>
-  <si>
-    <t>1 Day 18 Hours 29 Minutes</t>
+    <t>25 Min</t>
+  </si>
+  <si>
+    <t>41 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 40 Min</t>
+  </si>
+  <si>
+    <t>1 Hour 56 Min</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 47 Minutes</t>
+  </si>
+  <si>
+    <t>16 Hours 50 Minutes</t>
+  </si>
+  <si>
+    <t>3 Days 2 Hours</t>
+  </si>
+  <si>
+    <t>17 Hours 4 Minutes</t>
+  </si>
+  <si>
+    <t>1 Day 17 Hours 32 Minutes</t>
+  </si>
+  <si>
+    <t>3 hours 13 Minutes</t>
+  </si>
+  <si>
+    <t>14 Hours 4 Minutes</t>
+  </si>
+  <si>
+    <t>1 Day 15 Hours 12 Minutes</t>
+  </si>
+  <si>
+    <t>17 Hours 36 Minutes</t>
+  </si>
+  <si>
+    <t>18 Hours 35 Minutes</t>
+  </si>
+  <si>
+    <t>2 Hours 13 Minutes</t>
+  </si>
+  <si>
+    <t>10 Hours 43 Minutes</t>
+  </si>
+  <si>
+    <t>3 Days 21 Hours 41 Minutes</t>
+  </si>
+  <si>
+    <t>1 Day 5 Hours 57 Minutes</t>
+  </si>
+  <si>
+    <t>2 Days 4 Hours 45 Minutes</t>
+  </si>
+  <si>
+    <t>1 Hour 15 Minutes</t>
+  </si>
+  <si>
+    <t>8 Hours 40 Minutes</t>
+  </si>
+  <si>
+    <t>1 Day 15 Hours 39 minutes</t>
+  </si>
+  <si>
+    <t>24 Hours 25 Minutes</t>
+  </si>
+  <si>
+    <t>1 Day 5 Hours 40 Minutes</t>
+  </si>
+  <si>
+    <t>1 Hour 25 Minutes</t>
+  </si>
+  <si>
+    <t>2 Hours 22 Minutes</t>
+  </si>
+  <si>
+    <t>13 Hours 24 Minutes</t>
+  </si>
+  <si>
+    <t>7 Hours 53 Minutes</t>
+  </si>
+  <si>
+    <t>1 Day 3 Hours 45 Minutes</t>
+  </si>
+  <si>
+    <t>1 Hour 46 Minutes</t>
+  </si>
+  <si>
+    <t>1 Hour 54 Minutes</t>
+  </si>
+  <si>
+    <t>7 Hours 57 Minutes</t>
+  </si>
+  <si>
+    <t>9 Hours 51 Minutes</t>
+  </si>
+  <si>
+    <t>1 Day 4 Hours 41 Minutes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,18 +327,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF151920"/>
       <name val="Lato"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF151920"/>
+      <name val="Lato"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -268,36 +366,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFB0B5BF"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFB0B5BF"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFB0B5BF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFB0B5BF"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFB0B5BF"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -314,9 +388,8 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -324,19 +397,16 @@
     <xf numFmtId="17" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -669,17 +739,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{613A53DE-2B0F-44FD-9DA5-E08D04CBABE2}">
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -697,9 +767,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>45839</v>
+        <v>45931</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -717,9 +787,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46235</v>
+        <v>45962</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -737,192 +807,224 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46266</v>
+        <v>45992</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2">
+        <v>46023</v>
+      </c>
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>45931</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>23</v>
       </c>
-      <c r="F5" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2">
+        <v>46054</v>
+      </c>
+      <c r="B6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>45962</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>27</v>
       </c>
-      <c r="E6" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2">
+        <v>46082</v>
+      </c>
+      <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="F6" t="s">
+      <c r="C7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>45992</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>31</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>32</v>
       </c>
-      <c r="F7" t="s">
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>46023</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>35</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>36</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>37</v>
       </c>
-      <c r="F8" t="s">
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>46054</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
         <v>39</v>
       </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>41</v>
       </c>
-      <c r="F9" t="s">
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B10" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>46082</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>43</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>44</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>45</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>46</v>
       </c>
-      <c r="F10" t="s">
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B11" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>46235</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>46204</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>46235</v>
+        <v>46266</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <customProperties>
-    <customPr name="IbpWorksheetKeyString_GUID" r:id="rId1"/>
-  </customProperties>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{539BF5F2-EF88-4288-8ABD-042247B5A4B3}">
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -939,144 +1041,157 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="2">
-        <v>45839</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46113</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2">
         <v>46235</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="B6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2">
         <v>46266</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>45931</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>45962</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>45992</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>46143</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>46174</v>
-      </c>
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="B14" s="3"/>
-      <c r="D14" s="4"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="B15" s="3"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" spans="1:7" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="2:5" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="B17" s="6"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="2:5" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="B18" s="6"/>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="2:5" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="B19" s="6"/>
-    </row>
-    <row r="20" spans="2:5" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="B20" s="6"/>
+      <c r="B7" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.149999999999999">
+      <c r="B8" s="6"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:7" ht="16.899999999999999">
+      <c r="B9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="16.899999999999999">
+      <c r="B10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="16.899999999999999">
+      <c r="B11" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <customProperties>
-    <customPr name="IbpWorksheetKeyString_GUID" r:id="rId1"/>
-  </customProperties>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Whatfor_x003f_ xmlns="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73" xsi:nil="true"/>
-    <TaxCatchAll xmlns="dc4dcb21-90d3-4695-adc8-464bc3ea11a9" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1349,56 +1464,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Whatfor_x003f_ xmlns="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dc4dcb21-90d3-4695-adc8-464bc3ea11a9" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67E3F269-C870-4D23-A66D-7F6832BF1875}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="dc4dcb21-90d3-4695-adc8-464bc3ea11a9"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDD6048B-2CEB-4BEA-8F88-1C042992C094}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AB3424C-A238-4E06-BFA9-64918DF59714}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73"/>
-    <ds:schemaRef ds:uri="dc4dcb21-90d3-4695-adc8-464bc3ea11a9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AB3424C-A238-4E06-BFA9-64918DF59714}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDD6048B-2CEB-4BEA-8F88-1C042992C094}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67E3F269-C870-4D23-A66D-7F6832BF1875}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
